--- a/out/Attention-Mamba1_repeat_3_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.590389075499146</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.155749764472209</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.590389075499146</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.155749764472209</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.155749764472209</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.155749764472209</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.155749764472209</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.155749764472209</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.155749764472209</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.155749764472209</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5557497644722085</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001423804273493588</v>
+        <v>-0.0002417698469570605</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.641435969272138</v>
+        <v>2.787249264243427</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.285409453880325</v>
+        <v>5.578807112837994</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2461406683602616</v>
+        <v>0.4179604377765028</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.134051636960379</v>
+        <v>3.623737897673499</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3077558677037499</v>
+        <v>0.5225865427521634</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.503461906438717</v>
+        <v>4.251016988636552</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.4411665768513884</v>
+        <v>0.7491254933948605</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5557497644722085</v>
+        <v>1.85907883537967</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.078213084882226</v>
+        <v>5.226976237973024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4719608510502692</v>
+        <v>0.8014155432559043</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.581001474045256</v>
+        <v>6.080738381192688</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5001833739979021</v>
+        <v>0.8493396808137796</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.109443864807854</v>
+        <v>6.978062146603123</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2257234538873851</v>
+        <v>0.3832905354112329</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.060291604204249</v>
+        <v>6.894599071446994</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1090147543517167</v>
+        <v>0.1851124528814127</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.052419328219183</v>
+        <v>6.881231556875036</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05194167197720442</v>
+        <v>0.08820057264944936</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.047202571714971</v>
+        <v>6.872373244341244</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01538966256265722</v>
+        <v>0.02613321443578974</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.025984689540678</v>
+        <v>6.836345150288889</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01017846234395979</v>
+        <v>0.01728566635045794</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.030944796171262</v>
+        <v>6.844770585015984</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005207010257053409</v>
+        <v>0.008844692326210754</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.031174297901711</v>
+        <v>6.845163778141763</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002660641339994731</v>
+        <v>0.004521959632158726</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.031286477125388</v>
+        <v>6.845357763388421</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009971156303502737</v>
+        <v>0.001697234178744536</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.030617797461091</v>
+        <v>6.844225835034096</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005411539569451948</v>
+        <v>0.0009223067184386691</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.030702499696911</v>
+        <v>6.844373091534581</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002580556136348067</v>
+        <v>0.0004416382322137806</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.03067708130905</v>
+        <v>6.844333444610674</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001583365494942167</v>
+        <v>0.0002714913879992463</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.030734780685291</v>
+        <v>6.84443476975429</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>8.043764007129249e-05</v>
+        <v>0.0001401410512054487</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.030737224516092</v>
+        <v>6.844442415298181</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.596281836219229e-05</v>
+        <v>6.493651915496244e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.030729658725782</v>
+        <v>6.844433056121058</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.186207393301694e-05</v>
+        <v>3.97701232216949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.030736402489427</v>
+        <v>6.84444790945018</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>6.65611277636684e-06</v>
+        <v>1.598100299746031e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.030729001225969</v>
+        <v>6.844438791784667</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>1.468457874272584e-07</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.03072249449961</v>
+        <v>6.844431325207673</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-1.662115307266386e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.030717990596654</v>
+        <v>6.844427070029503</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.030712557465185</v>
+        <v>6.844421347750472</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.030707510844118</v>
+        <v>6.844416278395103</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.030707829124334</v>
+        <v>6.844411913421134</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.155749764472209</v>
+        <v>2.45907883537967</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.030708920370791</v>
+        <v>6.844413004667591</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.155749764472209</v>
+        <v>-0.6077945103300886</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.030708230763655</v>
+        <v>6.844412315060455</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.155749764472209</v>
+        <v>-0.6077945103300886</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.030708261076057</v>
+        <v>6.844412345372858</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.030708071623547</v>
+        <v>6.844412155920347</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.030708124670251</v>
+        <v>6.844412208967051</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.030708177716953</v>
+        <v>6.844412262013753</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.030708139826451</v>
+        <v>6.844412224123251</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.030708010998744</v>
+        <v>6.844412095295544</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.030707867014836</v>
+        <v>6.844411951311637</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.030707707874728</v>
+        <v>6.844411792171528</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.03070776092143</v>
+        <v>6.844411845218231</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.030707707874728</v>
+        <v>6.844411792171528</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.030707707874728</v>
+        <v>6.844411792171528</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.030707526000319</v>
+        <v>6.84441161029712</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.030707692718527</v>
+        <v>6.844411777015328</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.030707889749138</v>
+        <v>6.844411974045938</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.03070773060903</v>
+        <v>6.84441181490583</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.030707768499531</v>
+        <v>6.844411852796331</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.030707965530142</v>
+        <v>6.844412049826942</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.03070794279584</v>
+        <v>6.84441202709264</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.030707791233832</v>
+        <v>6.844411875530632</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.030707715452828</v>
+        <v>6.844411799749628</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.030707813968134</v>
+        <v>6.844411898264934</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.030707821546234</v>
+        <v>6.844411905843034</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.030708086779748</v>
+        <v>6.844412171076549</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.030707791233832</v>
+        <v>6.844411875530632</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.030708033733045</v>
+        <v>6.844412118029845</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.030708117092149</v>
+        <v>6.844412201388949</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.030707950373941</v>
+        <v>6.844412034670741</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.030708139826451</v>
+        <v>6.844412224123251</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.030707791233832</v>
+        <v>6.844411875530632</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.030707586625121</v>
+        <v>6.844411670921922</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.030707700296627</v>
+        <v>6.844411784593428</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.030707715452828</v>
+        <v>6.844411799749628</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.030707480531717</v>
+        <v>6.844411564828517</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.030707541156519</v>
+        <v>6.844411625453319</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.030707412328812</v>
+        <v>6.844411496625613</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.03070754873462</v>
+        <v>6.84441163303142</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.030707723030929</v>
+        <v>6.844411807327729</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.030707867014836</v>
+        <v>6.844411951311637</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.030707700296627</v>
+        <v>6.844411784593428</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.030707692718527</v>
+        <v>6.844411777015328</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.030707404750713</v>
+        <v>6.844411489047513</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.030707419906913</v>
+        <v>6.844411504203713</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.030707647249925</v>
+        <v>6.844411731546725</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.030707632093724</v>
+        <v>6.844411716390524</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.03070773818713</v>
+        <v>6.84441182248393</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.030707465375515</v>
+        <v>6.844411549672316</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.030707563890821</v>
+        <v>6.844411648187621</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.030707715452828</v>
+        <v>6.844411799749628</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.03070773060903</v>
+        <v>6.84441181490583</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5557497644722085</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.030707707874728</v>
+        <v>6.844411792171528</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.030707791233832</v>
+        <v>6.844411875530632</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.030707889749138</v>
+        <v>6.844411974045938</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.030707723030929</v>
+        <v>6.844411807327729</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.030707707874728</v>
+        <v>6.844411792171528</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.030707677562326</v>
+        <v>6.844411761859126</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.030707662406126</v>
+        <v>6.844411746702926</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.030707700296627</v>
+        <v>6.844411784593428</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.155749764472209</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.030707715452828</v>
+        <v>6.844411799749628</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.990389075499146</v>
+        <v>-1.207794510330089</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.030707707874728</v>
+        <v>6.844411792171528</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.5318763352092357</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.155749764472209</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.590389075499146</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001423804273493588</v>
+        <v>-0.0001416979264407419</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.641435969272138</v>
+        <v>1.633567741783418</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.285409453880325</v>
+        <v>3.269660836043158</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2461406683602616</v>
+        <v>0.244960769859575</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.134051636960379</v>
+        <v>2.123822055278779</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3077558677037499</v>
+        <v>0.3062807241450583</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.503461906438717</v>
+        <v>2.491461589814397</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.4411665768513884</v>
+        <v>0.4390518028808063</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.078213084882226</v>
+        <v>3.063457644803901</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4719608510502692</v>
+        <v>0.4696984617957199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.581001474045256</v>
+        <v>3.563835871754668</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5001833739979021</v>
+        <v>0.497785697393754</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.109443864807854</v>
+        <v>4.089745127368547</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2257234538873851</v>
+        <v>0.2246420928924615</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.060291604204249</v>
+        <v>4.040828481103459</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1090147543517167</v>
+        <v>0.1084912200914759</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.052419328219183</v>
+        <v>4.032993965598249</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05194167197720442</v>
+        <v>0.05169283638435568</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.047202571714971</v>
+        <v>4.027802200580881</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01538966256265722</v>
+        <v>0.01531627506471847</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.025984689540678</v>
+        <v>4.006685939559183</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01017846234395979</v>
+        <v>0.01012943869099189</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.030944796171262</v>
+        <v>4.011622143939611</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005207010257053409</v>
+        <v>0.005181427424000098</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.031174297901711</v>
+        <v>4.011850517366983</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002660641339994731</v>
+        <v>0.002648561394345209</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.031286477125388</v>
+        <v>4.011962142935712</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009971156303502737</v>
+        <v>0.0009925743208471756</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.030617797461091</v>
+        <v>4.011296719827219</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005411539569451948</v>
+        <v>0.0005386789390134189</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.155749764472209</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.030702499696911</v>
+        <v>4.011380947663612</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002580556136348067</v>
+        <v>0.00025646615373369</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.03067708130905</v>
+        <v>4.011355652466539</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001583365494942167</v>
+        <v>0.0001573525943767816</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.030734780685291</v>
+        <v>4.011412974135694</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>8.043764007129249e-05</v>
+        <v>7.940827091380704e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.030737224516092</v>
+        <v>4.011415373750388</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.030729658725782</v>
+        <v>4.011407807960079</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.155749764472209</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.030736402489427</v>
+        <v>4.011414551723723</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.030729001225969</v>
+        <v>4.011407150460266</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.03072249449961</v>
+        <v>4.011400643733906</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.030717990596654</v>
+        <v>4.011396139830951</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.155749764472209</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.030712557465185</v>
+        <v>4.011390706699483</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.030707510844118</v>
+        <v>4.011385660078415</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.030707829124334</v>
+        <v>4.011385978358631</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.030708920370791</v>
+        <v>4.011387069605088</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.030708230763655</v>
+        <v>4.011386379997952</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.030708261076057</v>
+        <v>4.011386410310354</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.030708071623547</v>
+        <v>4.011386220857844</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.030708124670251</v>
+        <v>4.011386273904547</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.030708177716953</v>
+        <v>4.011386326951249</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.030708139826451</v>
+        <v>4.011386289060748</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.030708010998744</v>
+        <v>4.01138616023304</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.155749764472209</v>
+        <v>0.5467998384952287</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.030707867014836</v>
+        <v>4.011386016249133</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.030707707874728</v>
+        <v>4.011385857109025</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.155749764472209</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.03070776092143</v>
+        <v>4.011385910155727</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.030707707874728</v>
+        <v>4.011385857109025</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.030707707874728</v>
+        <v>4.011385857109025</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.030707526000319</v>
+        <v>4.011385675234616</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.030707692718527</v>
+        <v>4.011385841952824</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.030707889749138</v>
+        <v>4.011386038983434</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.03070773060903</v>
+        <v>4.011385879843326</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.030707768499531</v>
+        <v>4.011385917733827</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.155749764472209</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.030707965530142</v>
+        <v>4.011386114764438</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.03070794279584</v>
+        <v>4.011386092030137</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.030707791233832</v>
+        <v>4.011385940468129</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.030707715452828</v>
+        <v>4.011385864687125</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.030707813968134</v>
+        <v>4.01138596320243</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.030707821546234</v>
+        <v>4.011385970780531</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.030708086779748</v>
+        <v>4.011386236014045</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.155749764472209</v>
+        <v>0.7467998384952288</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.030707791233832</v>
+        <v>4.011385940468129</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.155749764472209</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.030708033733045</v>
+        <v>4.011386182967342</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.590389075499146</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.030708117092149</v>
+        <v>4.011386266326446</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.030707950373941</v>
+        <v>4.011386099608238</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.030708139826451</v>
+        <v>4.011386289060748</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.030707791233832</v>
+        <v>4.011385940468129</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.030707586625121</v>
+        <v>4.011385735859418</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.030707700296627</v>
+        <v>4.011385849530924</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.030707715452828</v>
+        <v>4.011385864687125</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.030707480531717</v>
+        <v>4.011385629766013</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.030707541156519</v>
+        <v>4.011385690390816</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.155749764472209</v>
+        <v>-0.1723176106410809</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.030707412328812</v>
+        <v>4.011385561563109</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.155749764472209</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.03070754873462</v>
+        <v>4.011385697968917</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.030707723030929</v>
+        <v>4.011385872265225</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.030707867014836</v>
+        <v>4.011386016249133</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.155749764472209</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.030707700296627</v>
+        <v>4.011385849530924</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.030707692718527</v>
+        <v>4.011385841952824</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.030707404750713</v>
+        <v>4.011385553985009</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.030707419906913</v>
+        <v>4.01138556914121</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.590389075499146</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.030707647249925</v>
+        <v>4.011385796484221</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.155749764472209</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.030707632093724</v>
+        <v>4.011385781328021</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.03070773818713</v>
+        <v>4.011385887421427</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.030707465375515</v>
+        <v>4.011385614609813</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5557497644722085</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.030707563890821</v>
+        <v>4.011385713125117</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.030707715452828</v>
+        <v>4.011385864687125</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.03070773060903</v>
+        <v>4.011385879843326</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5557497644722085</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.030707707874728</v>
+        <v>4.011385857109025</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.155749764472209</v>
+        <v>0.02768238935891912</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.030707791233832</v>
+        <v>4.011385940468129</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.6914350597773905</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.030707889749138</v>
+        <v>4.011386038983434</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.030707723030929</v>
+        <v>4.011385872265225</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.030707707874728</v>
+        <v>4.011385857109025</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.030707677562326</v>
+        <v>4.011385826796623</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.590389075499146</v>
+        <v>-1.6105525089137</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.030707662406126</v>
+        <v>4.011385811640423</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.590389075499146</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.030707700296627</v>
+        <v>4.011385849530924</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.155749764472209</v>
+        <v>-0.8914350597773906</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.030707715452828</v>
+        <v>4.011385864687125</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.990389075499146</v>
+        <v>-0.3318763352092357</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.030707707874728</v>
+        <v>4.011385857109025</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0003846287727355957</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5318763352092357</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0006765425205230713</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.0009287409484386444</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.001181203871965408</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0002487227320671082</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>2.660602331161499e-05</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0001886487007141113</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.000217631459236145</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0008240267634391785</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0005254708230495453</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0005958899855613708</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0007440485060214996</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001335926353931427</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0004696249961853027</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.000425189733505249</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0006053075194358826</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001307491213083267</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0009135156869888306</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001181032508611679</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002043388783931732</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002365380525588989</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002895504236221313</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0003147721290588379</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0006224587559700012</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007592067122459412</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0006880238652229309</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0007653608918190002</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002039127051830292</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0006213933229446411</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0006811767816543579</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0007123276591300964</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0002303831279277802</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001024700701236725</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001313328742980957</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.003336686640977859</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01140516996383667</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001650918275117874</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002778679132461548</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001416979264407419</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.633567741783418</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001612622290849686</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.269660836043158</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.244960769859575</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001466192305088043</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.123822055278779</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3062807241450583</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001408834010362625</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.491461589814397</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.4390518028808063</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.007627945393323898</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.063457644803901</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4696984617957199</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01271408423781395</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.563835871754668</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.497785697393754</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02202025800943375</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.089745127368547</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2246420928924615</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.03363726660609245</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.040828481103459</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1084912200914759</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>7.625669240951538e-05</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.032993965598249</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05169283638435568</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01395614445209503</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.027802200580881</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01531627506471847</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0006936229765415192</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.006685939559183</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01012943869099189</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.003813289105892181</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.011622143939611</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005181427424000098</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0008882470428943634</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.011850517366983</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002648561394345209</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001685682684183121</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.011962142935712</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009925743208471756</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.001139864325523376</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.011296719827219</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005386789390134189</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0003630965948104858</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.011380947663612</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.00025646615373369</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.001312751322984695</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.011355652466539</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001573525943767816</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.001489952206611633</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.011412974135694</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.940827091380704e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>4.626810550689697e-06</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.011415373750388</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.596281836219229e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.03241958469152451</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.011407807960079</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.006915189325809479</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.02768238935891912</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.011414551723723</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002042524516582489</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1723176106410809</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.011407150460266</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.001503564417362213</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.011400643733906</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0009192489087581635</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.011396139830951</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.0009259060025215149</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5467998384952287</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.011390706699483</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.007264692336320877</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.011385660078415</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.035004623234272</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.011385978358631</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.1288591921329498</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.011387069605088</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.03713114559650421</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.011386379997952</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01280586794018745</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.011386410310354</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.009730242192745209</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7467998384952288</v>
+        <v>0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.011386220857844</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.005926698446273804</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.011386273904547</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0001743659377098083</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.011386326951249</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.0001221969723701477</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.011386289060748</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0006804391741752625</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.01138616023304</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0001405999064445496</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5467998384952287</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.011386016249133</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.0003754310309886932</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.011385857109025</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0003002621233463287</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.011385910155727</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001089774072170258</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.011385857109025</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0002984292805194855</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.011385857109025</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.002502065151929855</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.011385675234616</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.002797510474920273</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.011385841952824</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.001533214002847672</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.011386038983434</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.0005599036812782288</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.011385879843326</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.003242745995521545</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.011385917733827</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.003688961267471313</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.011386114764438</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001152954995632172</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6914350597773905</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.011386092030137</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0008754357695579529</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.011385940468129</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0004852786660194397</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.011385864687125</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0007831119000911713</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.01138596320243</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.003828588873147964</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.011385970780531</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.0005468204617500305</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.011386236014045</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0007969513535499573</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7467998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.011385940468129</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.00414353609085083</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.011386182967342</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0004942305386066437</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.011386266326446</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01386985927820206</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.011386099608238</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0007087960839271545</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1723176106410809</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.011386289060748</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0008104555308818817</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.011385940468129</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.001125417649745941</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.6105525089137</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.011385735859418</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-7.43865966796875e-05</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.6105525089137</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.011385849530924</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0005684345960617065</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.6105525089137</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.011385864687125</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0003724768757820129</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.6105525089137</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.011385629766013</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001549787819385529</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.011385690390816</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0004339180886745453</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1723176106410809</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.011385561563109</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.005161218345165253</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.02768238935891912</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.011385697968917</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.0007395073771476746</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6914350597773905</v>
+        <v>0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.011385872265225</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.001040678471326828</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6914350597773905</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.011386016249133</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0004721805453300476</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6914350597773905</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.011385849530924</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001788344234228134</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6914350597773905</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.011385841952824</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00123283639550209</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.011385553985009</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0009104050695896149</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.01138556914121</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.0002662092447280884</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.011385796484221</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.001011263579130173</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6914350597773905</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.011385781328021</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002343960106372833</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6914350597773905</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.011385887421427</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.0004368014633655548</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.011385614609813</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0008240155875682831</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.011385713125117</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-9.416788816452026e-05</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.011385864687125</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0002046041190624237</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8914350597773906</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.011385879843326</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0003160201013088226</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.011385857109025</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0006788037717342377</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.02768238935891912</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.011385940468129</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.00111568346619606</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6914350597773905</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.011386038983434</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0009630545973777771</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.6105525089137</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.011385872265225</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0001698024570941925</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.6105525089137</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.011385857109025</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.0003098435699939728</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.6105525089137</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.011385826796623</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-9.182840585708618e-06</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.6105525089137</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.011385811640423</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.0002905577421188354</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8914350597773906</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.011385849530924</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.000344201922416687</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8914350597773906</v>
+        <v>0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.011385864687125</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0001461021602153778</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3318763352092357</v>
+        <v>0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.011385857109025</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.0003846287727355957</v>
+        <v>-0.0003846511244773865</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.0006765425205230713</v>
+        <v>0.0006765574216842651</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.0009287409484386444</v>
+        <v>0.0009287521243095398</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.001181203871965408</v>
+        <v>0.001181166619062424</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0002487227320671082</v>
+        <v>-0.0002487264573574066</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>2.660602331161499e-05</v>
+        <v>2.655386924743652e-05</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.0001886487007141113</v>
+        <v>0.0001886263489723206</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.000217631459236145</v>
+        <v>0.0002176277339458466</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.0008240267634391785</v>
+        <v>0.0008240193128585815</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0005254708230495453</v>
+        <v>0.0005254857242107391</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.0005958899855613708</v>
+        <v>0.0005959309637546539</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0007440485060214996</v>
+        <v>0.0007440522313117981</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.001335926353931427</v>
+        <v>0.001335922628641129</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0004696249961853027</v>
+        <v>0.0004696361720561981</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.000425189733505249</v>
+        <v>0.0004251860082149506</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0006053075194358826</v>
+        <v>0.0006053224205970764</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0009135156869888306</v>
+        <v>0.0009135007858276367</v>
       </c>
       <c r="JB19" t="n">
         <v>0.5799999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.001181032508611679</v>
+        <v>0.001181017607450485</v>
       </c>
       <c r="JB20" t="n">
         <v>0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.002043388783931732</v>
+        <v>0.002043426036834717</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.002365380525588989</v>
+        <v>0.002365384250879288</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.002895504236221313</v>
+        <v>0.002895530313253403</v>
       </c>
       <c r="JB23" t="n">
         <v>0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0003147721290588379</v>
+        <v>0.000314764678478241</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0006224587559700012</v>
+        <v>0.0006224513053894043</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0007592067122459412</v>
+        <v>0.0007591880857944489</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0006880238652229309</v>
+        <v>0.0006880536675453186</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.16</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0007653608918190002</v>
+        <v>0.0007653720676898956</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.16</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.002039127051830292</v>
+        <v>0.002039112150669098</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.16</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.0006213933229446411</v>
+        <v>0.0006214044988155365</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0006811767816543579</v>
+        <v>0.0006811544299125671</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0007123276591300964</v>
+        <v>0.0007122941315174103</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0002303831279277802</v>
+        <v>0.0002304092049598694</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.001024700701236725</v>
+        <v>0.00102471187710762</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001313328742980957</v>
+        <v>0.001313284039497375</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.003336686640977859</v>
+        <v>0.003336690366268158</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001650918275117874</v>
+        <v>0.001650959253311157</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.002778679132461548</v>
+        <v>0.002778671681880951</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.001612622290849686</v>
+        <v>0.001612640917301178</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.001408834010362625</v>
+        <v>0.001408845186233521</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.02000000000000007</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.007627945393323898</v>
+        <v>0.007627960294485092</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.01271408423781395</v>
+        <v>0.01271406933665276</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.02202025800943375</v>
+        <v>0.02202025428414345</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.03363726660609245</v>
+        <v>0.03363724425435066</v>
       </c>
       <c r="JB46" t="n">
         <v>0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>7.625669240951538e-05</v>
+        <v>7.62157142162323e-05</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.1600000000000001</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01395614445209503</v>
+        <v>0.01395615935325623</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.4399999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.0006936229765415192</v>
+        <v>0.0006935857236385345</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.003813289105892181</v>
+        <v>0.003813277930021286</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0008882470428943634</v>
+        <v>-0.0008882507681846619</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.001139864325523376</v>
+        <v>0.001139868050813675</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.0003630965948104858</v>
+        <v>0.0003631226718425751</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.001489952206611633</v>
+        <v>0.001489955931901932</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>4.626810550689697e-06</v>
+        <v>4.641711711883545e-06</v>
       </c>
       <c r="JB57" t="n">
         <v>0.16</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.03241958469152451</v>
+        <v>0.03241955861449242</v>
       </c>
       <c r="JB58" t="n">
         <v>0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.006915189325809479</v>
+        <v>0.006915204226970673</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1600000000000001</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.002042524516582489</v>
+        <v>-0.002042554318904877</v>
       </c>
       <c r="JB60" t="n">
         <v>0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.001503564417362213</v>
+        <v>0.001503553241491318</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.0009192489087581635</v>
+        <v>0.0009192302823066711</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.1199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.0009259060025215149</v>
+        <v>0.0009258948266506195</v>
       </c>
       <c r="JB63" t="n">
         <v>0.16</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.007264692336320877</v>
+        <v>0.007264718413352966</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.035004623234272</v>
+        <v>0.03500461205840111</v>
       </c>
       <c r="JB65" t="n">
         <v>0.7199999999999999</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1288591921329498</v>
+        <v>0.1288591623306274</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>4.083061082323651</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.03713114559650421</v>
+        <v>0.03713113069534302</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>4.083060392716515</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.01280586794018745</v>
+        <v>0.01280588656663895</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>4.083060423028917</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.009730242192745209</v>
+        <v>0.00973023846745491</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>4.083060233576407</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.005926698446273804</v>
+        <v>0.005926724523305893</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>4.08306028662311</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0001743659377098083</v>
+        <v>-0.0001743920147418976</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>4.083060339669813</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.0001221969723701477</v>
+        <v>0.0001222118735313416</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.0006804391741752625</v>
+        <v>0.0006804168224334717</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.0001405999064445496</v>
+        <v>0.0001405850052833557</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.0003754310309886932</v>
+        <v>0.0003754571080207825</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.001089774072170258</v>
+        <v>-0.001089762896299362</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.0002984292805194855</v>
+        <v>-0.0002984441816806793</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.002502065151929855</v>
+        <v>0.002502076327800751</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.002797510474920273</v>
+        <v>0.002797525376081467</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.001533214002847672</v>
+        <v>-0.001533202826976776</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.0005599036812782288</v>
+        <v>-0.0005598925054073334</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.003242745995521545</v>
+        <v>0.003242701292037964</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001152954995632172</v>
+        <v>-0.001152969896793365</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.0008754357695579529</v>
+        <v>-0.0008754506707191467</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.0007831119000911713</v>
+        <v>0.0007831081748008728</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.003828588873147964</v>
+        <v>0.003828581422567368</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.0005468204617500305</v>
+        <v>0.0005468279123306274</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.0007969513535499573</v>
+        <v>0.0007969550788402557</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.00414353609085083</v>
+        <v>0.004143513739109039</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.0004942305386066437</v>
+        <v>-0.0004942379891872406</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.1199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.01386985927820206</v>
+        <v>0.01386987417936325</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.1199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.001125417649745941</v>
+        <v>-0.001125413924455643</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.3999999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-7.43865966796875e-05</v>
+        <v>-7.438287138938904e-05</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.0005684345960617065</v>
+        <v>-0.0005683973431587219</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.0003724768757820129</v>
+        <v>-0.0003724955022335052</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.8599999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.001549787819385529</v>
+        <v>-0.001549761742353439</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.5799999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.0004339180886745453</v>
+        <v>0.0004339329898357391</v>
       </c>
       <c r="JB102" t="n">
         <v>0.02000000000000007</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.005161218345165253</v>
+        <v>0.005161236971616745</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.0007395073771476746</v>
+        <v>-0.0007394962012767792</v>
       </c>
       <c r="JB104" t="n">
         <v>0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0004721805453300476</v>
+        <v>0.0004721730947494507</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.2599999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.001788344234228134</v>
+        <v>-0.00178837776184082</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.00123283639550209</v>
+        <v>-0.001232847571372986</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0009104050695896149</v>
+        <v>0.0009103752672672272</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.0002662092447280884</v>
+        <v>-0.0002661868929862976</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.001011263579130173</v>
+        <v>0.001011252403259277</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.0004368014633655548</v>
+        <v>-0.0004368163645267487</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0008240155875682831</v>
+        <v>0.0008240304887294769</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-9.416788816452026e-05</v>
+        <v>-9.41641628742218e-05</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.7199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.0002046041190624237</v>
+        <v>-0.0002046301960945129</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.5799999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.0003160201013088226</v>
+        <v>0.0003160163760185242</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.00111568346619606</v>
+        <v>-0.001115679740905762</v>
       </c>
       <c r="JB119" t="n">
         <v>0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.0009630545973777771</v>
+        <v>-0.0009630732238292694</v>
       </c>
       <c r="JB120" t="n">
         <v>0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.0001698024570941925</v>
+        <v>-0.0001698099076747894</v>
       </c>
       <c r="JB121" t="n">
         <v>0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.0003098435699939728</v>
+        <v>-0.0003098770976066589</v>
       </c>
       <c r="JB122" t="n">
         <v>0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-9.182840585708618e-06</v>
+        <v>-9.201467037200928e-06</v>
       </c>
       <c r="JB123" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.0002905577421188354</v>
+        <v>-0.0002905316650867462</v>
       </c>
       <c r="JB124" t="n">
         <v>0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.000344201922416687</v>
+        <v>0.0003441981971263885</v>
       </c>
       <c r="JB125" t="n">
         <v>0.3</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.0001461021602153778</v>
+        <v>-0.000146087259054184</v>
       </c>
       <c r="JB126" t="n">
         <v>0.3</v>
